--- a/Documentation/Best For Lists/Best Pets for Children and Families List.xlsx
+++ b/Documentation/Best For Lists/Best Pets for Children and Families List.xlsx
@@ -620,7 +620,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-12  |  Products shown: 16  |  Eliminated by dedup rule: 13</t>
+          <t>Generated: 2026-07-15  |  Products shown: 16  |  Eliminated by dedup rule: 13</t>
         </is>
       </c>
     </row>

--- a/Documentation/Best For Lists/Best Pets for Children and Families List.xlsx
+++ b/Documentation/Best For Lists/Best Pets for Children and Families List.xlsx
@@ -1588,22 +1588,20 @@
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>Budget Friendly</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="E18" s="12" t="inlineStr">
         <is>
-          <t>Dog</t>
-        </is>
-      </c>
-      <c r="F18" s="12" t="n">
-        <v>25.99</v>
-      </c>
+          <t>Unknown</t>
+        </is>
+      </c>
+      <c r="F18" s="12" t="n"/>
       <c r="G18" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H18" s="12" t="n">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="I18" s="17" t="n">
         <v>2.8</v>

--- a/Documentation/Best For Lists/Best Pets for Children and Families List.xlsx
+++ b/Documentation/Best For Lists/Best Pets for Children and Families List.xlsx
@@ -620,7 +620,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-15  |  Products shown: 16  |  Eliminated by dedup rule: 13</t>
+          <t>Generated: 2026-07-16  |  Products shown: 16  |  Eliminated by dedup rule: 13</t>
         </is>
       </c>
     </row>

--- a/Documentation/Best For Lists/Best Pets for Children and Families List.xlsx
+++ b/Documentation/Best For Lists/Best Pets for Children and Families List.xlsx
@@ -620,7 +620,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-07-16  |  Products shown: 16  |  Eliminated by dedup rule: 13</t>
+          <t>Generated: 2026-08-10  |  Products shown: 16  |  Eliminated by dedup rule: 13</t>
         </is>
       </c>
     </row>
@@ -780,13 +780,13 @@
         </is>
       </c>
       <c r="F5" s="8" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="G5" s="8" t="n">
-        <v>5</v>
+        <v>4.8</v>
       </c>
       <c r="H5" s="8" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="I5" s="9" t="n">
         <v>4.4</v>
@@ -843,13 +843,13 @@
         </is>
       </c>
       <c r="F6" s="12" t="n">
-        <v>178</v>
+        <v>199</v>
       </c>
       <c r="G6" s="12" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="H6" s="12" t="n">
-        <v>456</v>
+        <v>29</v>
       </c>
       <c r="I6" s="13" t="n">
         <v>4.4</v>
@@ -906,13 +906,13 @@
         </is>
       </c>
       <c r="F7" s="8" t="n">
-        <v>89</v>
+        <v>99</v>
       </c>
       <c r="G7" s="8" t="n">
         <v>5</v>
       </c>
       <c r="H7" s="8" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="I7" s="9" t="n">
         <v>4.25</v>
@@ -975,7 +975,7 @@
         <v>4.5</v>
       </c>
       <c r="H8" s="12" t="n">
-        <v>11640</v>
+        <v>12310</v>
       </c>
       <c r="I8" s="13" t="n">
         <v>4.1</v>
@@ -1038,7 +1038,7 @@
         <v>4.3</v>
       </c>
       <c r="H9" s="8" t="n">
-        <v>5164</v>
+        <v>5195</v>
       </c>
       <c r="I9" s="9" t="n">
         <v>4.1</v>
@@ -1095,13 +1095,13 @@
         </is>
       </c>
       <c r="F10" s="12" t="n">
-        <v>50.11</v>
+        <v>69.98999999999999</v>
       </c>
       <c r="G10" s="12" t="n">
         <v>4.8</v>
       </c>
       <c r="H10" s="12" t="n">
-        <v>772</v>
+        <v>1132</v>
       </c>
       <c r="I10" s="14" t="n">
         <v>3.75</v>
@@ -1161,10 +1161,10 @@
         <v>499</v>
       </c>
       <c r="G11" s="8" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="H11" s="8" t="n">
-        <v>1199</v>
+        <v>1231</v>
       </c>
       <c r="I11" s="15" t="n">
         <v>3.35</v>
@@ -1224,10 +1224,10 @@
         <v>349</v>
       </c>
       <c r="G12" s="12" t="n">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="H12" s="12" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="I12" s="14" t="n">
         <v>3.3</v>
@@ -1284,7 +1284,7 @@
         </is>
       </c>
       <c r="F13" s="8" t="n">
-        <v>119</v>
+        <v>139</v>
       </c>
       <c r="G13" s="8" t="n">
         <v>5</v>
@@ -1333,7 +1333,7 @@
       </c>
       <c r="C14" s="11" t="inlineStr">
         <is>
-          <t>Grey Tabby Cat</t>
+          <t>Original Border Collie</t>
         </is>
       </c>
       <c r="D14" s="12" t="inlineStr">
@@ -1343,17 +1343,17 @@
       </c>
       <c r="E14" s="12" t="inlineStr">
         <is>
-          <t>Cat</t>
+          <t>Dog</t>
         </is>
       </c>
       <c r="F14" s="12" t="n">
         <v>44.45</v>
       </c>
       <c r="G14" s="12" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="H14" s="12" t="n">
-        <v>848</v>
+        <v>441</v>
       </c>
       <c r="I14" s="14" t="n">
         <v>3</v>
@@ -1381,7 +1381,7 @@
       </c>
       <c r="Q14" s="11" t="inlineStr">
         <is>
-          <t>Breathing-only mechanism; no sensors, voice, or touch response. Sound Level Control=1 — no on/off switch or mute (battery must be removed to silence). Autonomous Interaction=3: breathing runs continuously without user direction. Review strength estimated; recommend manual verification. Previously scored as 'Calico Cat' — now matched to 'Grey Tabby Cat' per repo. Verify this is the correct product match before publishing. Review Strength=4: 848 reviews, 4.3★ (repo data, 2026-06-22). SOUND QUALITY UPDATE (2026-07-01, Tim-confirmed): Perfect Petzzz is NOT silent — manufacturer FAQ confirms the breathing mechanism emits sound as normal operation, and multiple Amazon reviews describe a mechanical/grinding noise rather than a soothing breath. Sound Quality rescored from 2 to 2 under the new merged rubric (was previously scored under 'absence of sound = neutral' logic, now scored on actual sound character; net score unchanged at 2, but rationale corrected). Sound appears to vary unit to unit per manufacturer's own FAQ and mixed review reports (some units near-silent/subtle snore, others audibly grinding) — no per-unit review data available to differentiate individual SKUs, so all 8 Perfect Petzzz products scored uniformly at 2 pending any future unit-specific verification. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=5, Familiar Form=4, Safety=5, Calmness=avg(Sound=2, Behavioral Realism=1)=1.5. Raw average of 4 sub-criteria=3.88, rounded=4, Evidence Tier D cap=3 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
+          <t>Breathing-only mechanism; no sensors, voice, or touch response. Sound Level Control=1 — no on/off switch or mute (battery must be removed to silence). Autonomous Interaction=3: breathing runs continuously without user direction. Review strength estimated; recommend manual verification. Product name updated: 'Original Border Collie' per repo. Review Strength=3: 403 reviews, 4.3★ (repo, 2026-06-22). SOUND QUALITY UPDATE (2026-07-01, Tim-confirmed): Perfect Petzzz is NOT silent — manufacturer FAQ confirms the breathing mechanism emits sound as normal operation, and multiple Amazon reviews describe a mechanical/grinding noise rather than a soothing breath. Sound Quality rescored from 2 to 2 under the new merged rubric (was previously scored under 'absence of sound = neutral' logic, now scored on actual sound character; net score unchanged at 2, but rationale corrected). Sound appears to vary unit to unit per manufacturer's own FAQ and mixed review reports (some units near-silent/subtle snore, others audibly grinding) — no per-unit review data available to differentiate individual SKUs, so all 8 Perfect Petzzz products scored uniformly at 2 pending any future unit-specific verification. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=5, Familiar Form=4, Safety=5, Calmness=avg(Sound=2, Behavioral Realism=1)=1.5. Raw average of 4 sub-criteria=3.88, rounded=4, Evidence Tier D cap=3 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="C15" s="7" t="inlineStr">
         <is>
-          <t>Original Chocolate Lab</t>
+          <t>Original Plush White Cat</t>
         </is>
       </c>
       <c r="D15" s="8" t="inlineStr">
@@ -1406,17 +1406,17 @@
       </c>
       <c r="E15" s="8" t="inlineStr">
         <is>
-          <t>Dog</t>
+          <t>Cat</t>
         </is>
       </c>
       <c r="F15" s="8" t="n">
-        <v>44.45</v>
+        <v>53.9</v>
       </c>
       <c r="G15" s="8" t="n">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="H15" s="8" t="n">
-        <v>553</v>
+        <v>55</v>
       </c>
       <c r="I15" s="15" t="n">
         <v>3</v>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="Q15" s="7" t="inlineStr">
         <is>
-          <t>Breathing-only mechanism; no sensors, voice, or touch response. Sound Level Control=1 — no on/off switch or mute (battery must be removed to silence). Autonomous Interaction=3: breathing runs continuously without user direction. Review strength estimated; recommend manual verification. Product name updated: 'Original Chocolate Lab' per repo. Review Strength=4: 553 reviews, 4.3★ (repo, 2026-06-22). SOUND QUALITY UPDATE (2026-07-01, Tim-confirmed): Perfect Petzzz is NOT silent — manufacturer FAQ confirms the breathing mechanism emits sound as normal operation, and multiple Amazon reviews describe a mechanical/grinding noise rather than a soothing breath. Sound Quality rescored from 2 to 2 under the new merged rubric (was previously scored under 'absence of sound = neutral' logic, now scored on actual sound character; net score unchanged at 2, but rationale corrected). Sound appears to vary unit to unit per manufacturer's own FAQ and mixed review reports (some units near-silent/subtle snore, others audibly grinding) — no per-unit review data available to differentiate individual SKUs, so all 8 Perfect Petzzz products scored uniformly at 2 pending any future unit-specific verification. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=5, Familiar Form=4, Safety=5, Calmness=avg(Sound=2, Behavioral Realism=1)=1.5. Raw average of 4 sub-criteria=3.88, rounded=4, Evidence Tier D cap=3 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
+          <t>Breathing-only mechanism; no sensors, voice, or touch response. Sound Level Control=1 — no on/off switch or mute (battery must be removed to silence). Autonomous Interaction=3: breathing runs continuously without user direction. Review strength estimated; recommend manual verification. White coat: higher visual contrast against most furniture/bedding. Product name updated: 'Original Plush White Cat' per repo. Review Strength=2: 54 reviews, 4.0★ (repo, 2026-06-22). SOUND QUALITY UPDATE (2026-07-01, Tim-confirmed): Perfect Petzzz is NOT silent — manufacturer FAQ confirms the breathing mechanism emits sound as normal operation, and multiple Amazon reviews describe a mechanical/grinding noise rather than a soothing breath. Sound Quality rescored from 2 to 2 under the new merged rubric (was previously scored under 'absence of sound = neutral' logic, now scored on actual sound character; net score unchanged at 2, but rationale corrected). Sound appears to vary unit to unit per manufacturer's own FAQ and mixed review reports (some units near-silent/subtle snore, others audibly grinding) — no per-unit review data available to differentiate individual SKUs, so all 8 Perfect Petzzz products scored uniformly at 2 pending any future unit-specific verification. DEMENTIA SUITABILITY EVIDENCE TIER (2026-07-02): Tier D — no dementia-specific evidence found (independent or manufacturer); score reflects general sub-criteria judgment only (simplicity, familiar form, calmness, safety). Capped at 3. Score is provisional pending dementia consultant review. DEMENTIA SUITABILITY RECALCULATED (2026-07-02, Tim-directed methodology): Simplicity=5, Familiar Form=4, Safety=5, Calmness=avg(Sound=2, Behavioral Realism=1)=1.5. Raw average of 4 sub-criteria=3.88, rounded=4, Evidence Tier D cap=3 -&gt; Final=3 (no change). This is a first-pass 'best effort' score pending dementia care consultant review (consultant search in progress as of 2026-07-02). Products in the 'Ai &amp; Robotic Pets' Type category are excluded from memory-care-relevant Best For lists via a separate Type filter in the Best For Weighting Table, independent of this score.</t>
         </is>
       </c>
     </row>
@@ -1537,10 +1537,10 @@
         <v>69.98999999999999</v>
       </c>
       <c r="G17" s="8" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="H17" s="8" t="n">
-        <v>283</v>
+        <v>346</v>
       </c>
       <c r="I17" s="16" t="n">
         <v>2.85</v>
@@ -1658,7 +1658,7 @@
         </is>
       </c>
       <c r="F19" s="8" t="n">
-        <v>359</v>
+        <v>319</v>
       </c>
       <c r="G19" s="8" t="n">
         <v>5</v>
@@ -1721,13 +1721,13 @@
         </is>
       </c>
       <c r="F20" s="12" t="n">
-        <v>179</v>
+        <v>139</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>4.5</v>
       </c>
       <c r="H20" s="12" t="n">
-        <v>72</v>
+        <v>75</v>
       </c>
       <c r="I20" s="17" t="n">
         <v>2.65</v>
@@ -2014,7 +2014,7 @@
         <v>4</v>
       </c>
       <c r="F7" s="19" t="n">
-        <v>4</v>
+        <v>4.95</v>
       </c>
       <c r="G7" s="19" t="inlineStr">
         <is>
@@ -2023,7 +2023,7 @@
       </c>
       <c r="H7" s="19" t="inlineStr">
         <is>
-          <t>score=4.00 rating=4</t>
+          <t>score=4.00 rating=4.95</t>
         </is>
       </c>
     </row>
@@ -2035,7 +2035,7 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Original Siamese Cat</t>
+          <t>Grey Tabby Cat</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -2052,16 +2052,16 @@
         <v>3</v>
       </c>
       <c r="F8" s="20" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="G8" s="20" t="inlineStr">
         <is>
-          <t>Grey Tabby Cat</t>
+          <t>Original Plush White Cat</t>
         </is>
       </c>
       <c r="H8" s="20" t="inlineStr">
         <is>
-          <t>score=3.00 rating=4.1</t>
+          <t>score=3.00 rating=4.2</t>
         </is>
       </c>
     </row>
@@ -2073,33 +2073,33 @@
       </c>
       <c r="B9" s="19" t="inlineStr">
         <is>
+          <t>Original Siamese Cat</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>Budget Friendly</t>
+        </is>
+      </c>
+      <c r="D9" s="19" t="inlineStr">
+        <is>
+          <t>Cat</t>
+        </is>
+      </c>
+      <c r="E9" s="19" t="n">
+        <v>3</v>
+      </c>
+      <c r="F9" s="19" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="G9" s="19" t="inlineStr">
+        <is>
           <t>Original Plush White Cat</t>
         </is>
       </c>
-      <c r="C9" s="19" t="inlineStr">
-        <is>
-          <t>Budget Friendly</t>
-        </is>
-      </c>
-      <c r="D9" s="19" t="inlineStr">
-        <is>
-          <t>Cat</t>
-        </is>
-      </c>
-      <c r="E9" s="19" t="n">
-        <v>3</v>
-      </c>
-      <c r="F9" s="19" t="n">
-        <v>4</v>
-      </c>
-      <c r="G9" s="19" t="inlineStr">
-        <is>
-          <t>Grey Tabby Cat</t>
-        </is>
-      </c>
       <c r="H9" s="19" t="inlineStr">
         <is>
-          <t>score=3.00 rating=4</t>
+          <t>score=3.00 rating=4.1</t>
         </is>
       </c>
     </row>
@@ -2187,7 +2187,7 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Original Border Collie</t>
+          <t>Original Chocolate Lab</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -2208,7 +2208,7 @@
       </c>
       <c r="G12" s="20" t="inlineStr">
         <is>
-          <t>Original Chocolate Lab</t>
+          <t>Original Border Collie</t>
         </is>
       </c>
       <c r="H12" s="20" t="inlineStr">

--- a/Documentation/Best For Lists/Best Pets for Children and Families List.xlsx
+++ b/Documentation/Best For Lists/Best Pets for Children and Families List.xlsx
@@ -620,7 +620,7 @@
     <row r="2" ht="20" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Generated: 2026-08-10  |  Products shown: 16  |  Eliminated by dedup rule: 13</t>
+          <t>Generated: 2026-08-13  |  Products shown: 16  |  Eliminated by dedup rule: 13</t>
         </is>
       </c>
     </row>
